--- a/upload/internacoes-via-urgencia.xlsx
+++ b/upload/internacoes-via-urgencia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="12">
   <si>
     <t>unidade</t>
   </si>
@@ -39,10 +39,10 @@
     <t>CSSI</t>
   </si>
   <si>
-    <t>HAC</t>
+    <t>IRS</t>
   </si>
   <si>
-    <t>HJK</t>
+    <t>MOV</t>
   </si>
   <si>
     <t>HRBJA</t>
@@ -51,10 +51,10 @@
     <t>HRJP</t>
   </si>
   <si>
-    <t>IRS</t>
+    <t>HAC</t>
   </si>
   <si>
-    <t>MOV</t>
+    <t>HJK</t>
   </si>
 </sst>
 </file>
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -470,240 +470,240 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E6" s="2">
-        <v>2472</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2">
-        <v>3441</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C8" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="E8" s="2">
-        <v>3014</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C9" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D9" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E9" s="2">
-        <v>3049</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C10" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2">
-        <v>3039</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C11" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="2">
-        <v>71</v>
+        <v>297</v>
       </c>
       <c r="E11" s="2">
-        <v>2640</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C12" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D12" s="2">
-        <v>65</v>
+        <v>341</v>
       </c>
       <c r="E12" s="2">
-        <v>2465</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B13" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C13" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D13" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="E13" s="2">
-        <v>2488</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B14" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C14" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2">
-        <v>54</v>
+        <v>340</v>
       </c>
       <c r="E14" s="2">
-        <v>2698</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C15" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2">
-        <v>65</v>
+        <v>387</v>
       </c>
       <c r="E15" s="2">
-        <v>2544</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C16" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2">
-        <v>71</v>
+        <v>350</v>
       </c>
       <c r="E16" s="2">
-        <v>2491</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17" s="2">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C17" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2">
-        <v>74</v>
+        <v>366</v>
       </c>
       <c r="E17" s="2">
-        <v>2409</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C18" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D18" s="2">
-        <v>61</v>
+        <v>365</v>
       </c>
       <c r="E18" s="2">
-        <v>2408</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B19" s="2">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C19" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2">
-        <v>65</v>
+        <v>378</v>
       </c>
       <c r="E19" s="2">
-        <v>2338</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -711,16 +711,16 @@
         <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E20" s="2">
-        <v>2476</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -728,16 +728,16 @@
         <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C21" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2">
-        <v>2597</v>
+        <v>3441</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -745,16 +745,16 @@
         <v>5</v>
       </c>
       <c r="B22" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C22" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="2">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="E22" s="2">
-        <v>2957</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -762,16 +762,16 @@
         <v>5</v>
       </c>
       <c r="B23" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C23" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2">
-        <v>2672</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -779,16 +779,16 @@
         <v>5</v>
       </c>
       <c r="B24" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C24" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" s="2">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="E24" s="2">
-        <v>2625</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -796,16 +796,16 @@
         <v>5</v>
       </c>
       <c r="B25" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C25" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D25" s="2">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2">
-        <v>2793</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -813,16 +813,16 @@
         <v>5</v>
       </c>
       <c r="B26" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C26" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26" s="2">
-        <v>2707</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -830,16 +830,16 @@
         <v>5</v>
       </c>
       <c r="B27" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C27" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E27" s="2">
-        <v>2603</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -847,16 +847,16 @@
         <v>5</v>
       </c>
       <c r="B28" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C28" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2">
-        <v>2433</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -864,16 +864,16 @@
         <v>5</v>
       </c>
       <c r="B29" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C29" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2">
-        <v>2580</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -881,16 +881,16 @@
         <v>5</v>
       </c>
       <c r="B30" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C30" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="E30" s="2">
-        <v>2280</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -898,548 +898,548 @@
         <v>5</v>
       </c>
       <c r="B31" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C31" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E31" s="2">
-        <v>2243</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B32" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C32" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32" s="2">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E32" s="2">
-        <v>2825</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B33" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C33" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2">
-        <v>70</v>
+        <v>321</v>
       </c>
       <c r="E33" s="2">
-        <v>179</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C34" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2">
-        <v>125</v>
+        <v>362</v>
       </c>
       <c r="E34" s="2">
-        <v>285</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B35" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C35" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2">
-        <v>101</v>
+        <v>342</v>
       </c>
       <c r="E35" s="2">
-        <v>282</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B36" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2">
-        <v>110</v>
+        <v>201</v>
       </c>
       <c r="E36" s="2">
-        <v>254</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B37" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D37" s="2">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="E37" s="2">
-        <v>271</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B38" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2">
-        <v>137</v>
+        <v>254</v>
       </c>
       <c r="E38" s="2">
-        <v>256</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C39" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D39" s="2">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E39" s="2">
-        <v>705</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C40" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D40" s="2">
-        <v>865</v>
+        <v>99</v>
       </c>
       <c r="E40" s="2">
-        <v>5010</v>
+        <v>313</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B41" s="2">
         <v>2024</v>
       </c>
       <c r="C41" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D41" s="2">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="E41" s="2">
-        <v>409</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2">
         <v>2024</v>
       </c>
       <c r="C42" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2">
-        <v>321</v>
+        <v>74</v>
       </c>
       <c r="E42" s="2">
-        <v>2169</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2">
         <v>2024</v>
       </c>
       <c r="C43" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D43" s="2">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2">
-        <v>2014</v>
+        <v>344</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2">
         <v>2024</v>
       </c>
       <c r="C44" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D44" s="2">
-        <v>342</v>
+        <v>80</v>
       </c>
       <c r="E44" s="2">
-        <v>2167</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B45" s="2">
         <v>2024</v>
       </c>
       <c r="C45" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D45" s="2">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="E45" s="2">
-        <v>2361</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2">
         <v>2024</v>
       </c>
       <c r="C46" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D46" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2">
-        <v>2262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2">
         <v>2024</v>
       </c>
       <c r="C47" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D47" s="2">
-        <v>254</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2">
-        <v>2346</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B48" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C48" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="E48" s="2">
-        <v>2286</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B49" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C49" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2">
-        <v>233</v>
+        <v>56</v>
       </c>
       <c r="E49" s="2">
-        <v>2139</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B50" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C50" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D50" s="2">
-        <v>263</v>
+        <v>84</v>
       </c>
       <c r="E50" s="2">
-        <v>2491</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B51" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C51" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D51" s="2">
-        <v>254</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2">
-        <v>2423</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B52" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C52" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2">
-        <v>274</v>
+        <v>53</v>
       </c>
       <c r="E52" s="2">
-        <v>2797</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B53" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C53" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D53" s="2">
-        <v>253</v>
+        <v>366</v>
       </c>
       <c r="E53" s="2">
-        <v>2766</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B54" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C54" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D54" s="2">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="E54" s="2">
-        <v>2794</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B55" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C55" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D55" s="2">
-        <v>260</v>
+        <v>430</v>
       </c>
       <c r="E55" s="2">
-        <v>2854</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B56" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C56" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D56" s="2">
-        <v>233</v>
+        <v>390</v>
       </c>
       <c r="E56" s="2">
-        <v>2916</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B57" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C57" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>237</v>
+        <v>392</v>
       </c>
       <c r="E57" s="2">
-        <v>2896</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B58" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C58" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D58" s="2">
-        <v>249</v>
+        <v>344</v>
       </c>
       <c r="E58" s="2">
-        <v>2719</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B59" s="2">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C59" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D59" s="2">
-        <v>255</v>
+        <v>353</v>
       </c>
       <c r="E59" s="2">
-        <v>2896</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B60" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C60" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2">
-        <v>264</v>
+        <v>343</v>
       </c>
       <c r="E60" s="2">
-        <v>2966</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B61" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C61" s="2">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D61" s="2">
-        <v>304</v>
+        <v>382</v>
       </c>
       <c r="E61" s="2">
-        <v>2783</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B62" s="2">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C62" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D62" s="2">
-        <v>292</v>
+        <v>357</v>
       </c>
       <c r="E62" s="2">
-        <v>3285</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B63" s="2">
         <v>2024</v>
@@ -1448,15 +1448,15 @@
         <v>11</v>
       </c>
       <c r="D63" s="2">
-        <v>102</v>
+        <v>321</v>
       </c>
       <c r="E63" s="2">
-        <v>234</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B64" s="2">
         <v>2024</v>
@@ -1465,15 +1465,15 @@
         <v>12</v>
       </c>
       <c r="D64" s="2">
-        <v>99</v>
+        <v>326</v>
       </c>
       <c r="E64" s="2">
-        <v>313</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B65" s="2">
         <v>2025</v>
@@ -1482,15 +1482,15 @@
         <v>1</v>
       </c>
       <c r="D65" s="2">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="E65" s="2">
-        <v>353</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B66" s="2">
         <v>2025</v>
@@ -1499,15 +1499,15 @@
         <v>2</v>
       </c>
       <c r="D66" s="2">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="E66" s="2">
-        <v>348</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B67" s="2">
         <v>2025</v>
@@ -1516,15 +1516,15 @@
         <v>3</v>
       </c>
       <c r="D67" s="2">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="E67" s="2">
-        <v>386</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B68" s="2">
         <v>2025</v>
@@ -1533,15 +1533,15 @@
         <v>4</v>
       </c>
       <c r="D68" s="2">
-        <v>149</v>
+        <v>61</v>
       </c>
       <c r="E68" s="2">
-        <v>314</v>
+        <v>2597</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B69" s="2">
         <v>2025</v>
@@ -1550,15 +1550,15 @@
         <v>5</v>
       </c>
       <c r="D69" s="2">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="E69" s="2">
-        <v>361</v>
+        <v>2957</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B70" s="2">
         <v>2025</v>
@@ -1567,15 +1567,15 @@
         <v>6</v>
       </c>
       <c r="D70" s="2">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="E70" s="2">
-        <v>313</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B71" s="2">
         <v>2025</v>
@@ -1584,15 +1584,15 @@
         <v>7</v>
       </c>
       <c r="D71" s="2">
-        <v>145</v>
+        <v>63</v>
       </c>
       <c r="E71" s="2">
-        <v>304</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B72" s="2">
         <v>2025</v>
@@ -1601,15 +1601,15 @@
         <v>8</v>
       </c>
       <c r="D72" s="2">
-        <v>160</v>
+        <v>62</v>
       </c>
       <c r="E72" s="2">
-        <v>333</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B73" s="2">
         <v>2025</v>
@@ -1618,15 +1618,15 @@
         <v>9</v>
       </c>
       <c r="D73" s="2">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="E73" s="2">
-        <v>317</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B74" s="2">
         <v>2025</v>
@@ -1635,15 +1635,15 @@
         <v>10</v>
       </c>
       <c r="D74" s="2">
-        <v>154</v>
+        <v>61</v>
       </c>
       <c r="E74" s="2">
-        <v>405</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B75" s="2">
         <v>2025</v>
@@ -1652,15 +1652,15 @@
         <v>11</v>
       </c>
       <c r="D75" s="2">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="E75" s="2">
-        <v>383</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B76" s="2">
         <v>2025</v>
@@ -1669,585 +1669,585 @@
         <v>12</v>
       </c>
       <c r="D76" s="2">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="E76" s="2">
-        <v>372</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B77" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C77" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D77" s="2">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="E77" s="2">
-        <v>404</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B78" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C78" s="2">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D78" s="2">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="E78" s="2">
-        <v>359</v>
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B79" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C79" s="2">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D79" s="2">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="E79" s="2">
-        <v>379</v>
+        <v>282</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B80" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C80" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D80" s="2">
-        <v>86</v>
+        <v>267</v>
       </c>
       <c r="E80" s="2">
-        <v>273</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B81" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C81" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D81" s="2">
-        <v>76</v>
+        <v>233</v>
       </c>
       <c r="E81" s="2">
-        <v>312</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B82" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C82" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D82" s="2">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="E82" s="2">
-        <v>293</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B83" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C83" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D83" s="2">
-        <v>84</v>
+        <v>254</v>
       </c>
       <c r="E83" s="2">
-        <v>276</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B84" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C84" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D84" s="2">
-        <v>79</v>
+        <v>274</v>
       </c>
       <c r="E84" s="2">
-        <v>271</v>
+        <v>2797</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B85" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C85" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D85" s="2">
-        <v>95</v>
+        <v>253</v>
       </c>
       <c r="E85" s="2">
-        <v>312</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B86" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C86" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D86" s="2">
-        <v>74</v>
+        <v>287</v>
       </c>
       <c r="E86" s="2">
-        <v>303</v>
+        <v>2795</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B87" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C87" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="E87" s="2">
-        <v>344</v>
+        <v>2854</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B88" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C88" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D88" s="2">
-        <v>80</v>
+        <v>233</v>
       </c>
       <c r="E88" s="2">
-        <v>299</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
+        <v>8</v>
+      </c>
+      <c r="B89" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C89" s="2">
         <v>10</v>
       </c>
-      <c r="B89" s="2">
-        <v>2024</v>
-      </c>
-      <c r="C89" s="2">
-        <v>5</v>
-      </c>
       <c r="D89" s="2">
-        <v>69</v>
+        <v>237</v>
       </c>
       <c r="E89" s="2">
-        <v>318</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B90" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C90" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D90" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="E90" s="2">
-        <v>265</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B91" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C91" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D91" s="2">
-        <v>78</v>
+        <v>255</v>
       </c>
       <c r="E91" s="2">
-        <v>285</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B92" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C92" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D92" s="2">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="E92" s="2">
-        <v>229</v>
+        <v>353</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B93" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C93" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D93" s="2">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="E93" s="2">
-        <v>277</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B94" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C94" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D94" s="2">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="E94" s="2">
-        <v>283</v>
+        <v>386</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B95" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C95" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D95" s="2">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="E95" s="2">
-        <v>258</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B96" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C96" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D96" s="2">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="E96" s="2">
-        <v>257</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B97" s="2">
         <v>2025</v>
       </c>
       <c r="C97" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D97" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="E97" s="2">
-        <v>241</v>
+        <v>313</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B98" s="2">
         <v>2025</v>
       </c>
       <c r="C98" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D98" s="2">
-        <v>55</v>
+        <v>145</v>
       </c>
       <c r="E98" s="2">
-        <v>228</v>
+        <v>304</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B99" s="2">
         <v>2025</v>
       </c>
       <c r="C99" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D99" s="2">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="E99" s="2">
-        <v>300</v>
+        <v>333</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B100" s="2">
         <v>2025</v>
       </c>
       <c r="C100" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="E100" s="2">
-        <v>278</v>
+        <v>317</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C101" s="2">
         <v>10</v>
       </c>
-      <c r="B101" s="2">
-        <v>2025</v>
-      </c>
-      <c r="C101" s="2">
-        <v>5</v>
-      </c>
       <c r="D101" s="2">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="E101" s="2">
-        <v>258</v>
+        <v>405</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B102" s="2">
         <v>2025</v>
       </c>
       <c r="C102" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D102" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="E102" s="2">
-        <v>230</v>
+        <v>383</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B103" s="2">
         <v>2025</v>
       </c>
       <c r="C103" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D103" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="E103" s="2">
-        <v>249</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B104" s="2">
         <v>2025</v>
       </c>
       <c r="C104" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D104" s="2">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E104" s="2">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B105" s="2">
         <v>2025</v>
       </c>
       <c r="C105" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D105" s="2">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E105" s="2">
-        <v>269</v>
+        <v>228</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B106" s="2">
         <v>2025</v>
       </c>
       <c r="C106" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D106" s="2">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E106" s="2">
-        <v>249</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B107" s="2">
         <v>2025</v>
       </c>
       <c r="C107" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D107" s="2">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E107" s="2">
-        <v>233</v>
+        <v>278</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B108" s="2">
         <v>2025</v>
       </c>
       <c r="C108" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D108" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E108" s="2">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B109" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C109" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D109" s="2">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="E109" s="2">
-        <v>248</v>
+        <v>230</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B110" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C110" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D110" s="2">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E110" s="2">
         <v>249</v>
@@ -2255,427 +2255,427 @@
     </row>
     <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B111" s="2">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C111" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D111" s="2">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E111" s="2">
-        <v>228</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B112" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C112" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D112" s="2">
-        <v>297</v>
+        <v>74</v>
       </c>
       <c r="E112" s="2">
-        <v>1061</v>
+        <v>269</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B113" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C113" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D113" s="2">
-        <v>341</v>
+        <v>94</v>
       </c>
       <c r="E113" s="2">
-        <v>1358</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" t="s">
+        <v>6</v>
+      </c>
+      <c r="B114" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C114" s="2">
         <v>11</v>
       </c>
-      <c r="B114" s="2">
-        <v>2023</v>
-      </c>
-      <c r="C114" s="2">
-        <v>6</v>
-      </c>
       <c r="D114" s="2">
-        <v>343</v>
+        <v>65</v>
       </c>
       <c r="E114" s="2">
-        <v>1258</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B115" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C115" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D115" s="2">
-        <v>340</v>
+        <v>68</v>
       </c>
       <c r="E115" s="2">
-        <v>1266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B116" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C116" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D116" s="2">
-        <v>387</v>
+        <v>402</v>
       </c>
       <c r="E116" s="2">
-        <v>1443</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B117" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C117" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D117" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E117" s="2">
-        <v>1392</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B118" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C118" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D118" s="2">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="E118" s="2">
-        <v>1500</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B119" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C119" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D119" s="2">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="E119" s="2">
-        <v>1424</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B120" s="2">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C120" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D120" s="2">
-        <v>378</v>
+        <v>409</v>
       </c>
       <c r="E120" s="2">
-        <v>1304</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B121" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C121" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D121" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="E121" s="2">
-        <v>1534</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B122" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C122" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D122" s="2">
-        <v>385</v>
+        <v>338</v>
       </c>
       <c r="E122" s="2">
-        <v>1510</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B123" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C123" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D123" s="2">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="E123" s="2">
-        <v>1540</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B124" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C124" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D124" s="2">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="E124" s="2">
-        <v>1402</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B125" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C125" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D125" s="2">
         <v>392</v>
       </c>
       <c r="E125" s="2">
-        <v>1363</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126" s="2">
+        <v>2025</v>
+      </c>
+      <c r="C126" s="2">
         <v>11</v>
       </c>
-      <c r="B126" s="2">
-        <v>2024</v>
-      </c>
-      <c r="C126" s="2">
-        <v>6</v>
-      </c>
       <c r="D126" s="2">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="E126" s="2">
-        <v>1129</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B127" s="2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C127" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D127" s="2">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="E127" s="2">
-        <v>1262</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B128" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C128" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D128" s="2">
-        <v>343</v>
+        <v>60</v>
       </c>
       <c r="E128" s="2">
-        <v>1257</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B129" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C129" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D129" s="2">
-        <v>382</v>
+        <v>69</v>
       </c>
       <c r="E129" s="2">
-        <v>1297</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B130" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C130" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D130" s="2">
-        <v>357</v>
+        <v>70</v>
       </c>
       <c r="E130" s="2">
-        <v>1315</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B131" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C131" s="2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D131" s="2">
-        <v>321</v>
+        <v>64</v>
       </c>
       <c r="E131" s="2">
-        <v>1329</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B132" s="2">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C132" s="2">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D132" s="2">
-        <v>326</v>
+        <v>110</v>
       </c>
       <c r="E132" s="2">
-        <v>1261</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B133" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C133" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D133" s="2">
-        <v>402</v>
+        <v>106</v>
       </c>
       <c r="E133" s="2">
-        <v>1450</v>
+        <v>271</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B134" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C134" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D134" s="2">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="E134" s="2">
-        <v>1356</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B135" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C135" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D135" s="2">
-        <v>396</v>
+        <v>124</v>
       </c>
       <c r="E135" s="2">
-        <v>1578</v>
+        <v>310</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2683,16 +2683,16 @@
         <v>11</v>
       </c>
       <c r="B136" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C136" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D136" s="2">
-        <v>402</v>
+        <v>93</v>
       </c>
       <c r="E136" s="2">
-        <v>1524</v>
+        <v>705</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2700,16 +2700,16 @@
         <v>11</v>
       </c>
       <c r="B137" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C137" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D137" s="2">
-        <v>409</v>
+        <v>864</v>
       </c>
       <c r="E137" s="2">
-        <v>1432</v>
+        <v>5010</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2717,169 +2717,288 @@
         <v>11</v>
       </c>
       <c r="B138" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C138" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D138" s="2">
-        <v>380</v>
+        <v>776</v>
       </c>
       <c r="E138" s="2">
-        <v>1308</v>
+        <v>5115</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B139" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C139" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D139" s="2">
-        <v>338</v>
+        <v>264</v>
       </c>
       <c r="E139" s="2">
-        <v>1389</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B140" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C140" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="E140" s="2">
-        <v>1401</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B141" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C141" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2">
-        <v>374</v>
+        <v>293</v>
       </c>
       <c r="E141" s="2">
-        <v>1377</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B142" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C142" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D142" s="2">
-        <v>392</v>
+        <v>263</v>
       </c>
       <c r="E142" s="2">
-        <v>1446</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B143" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C143" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D143" s="2">
-        <v>362</v>
+        <v>157</v>
       </c>
       <c r="E143" s="2">
-        <v>1359</v>
+        <v>404</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B144" s="2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C144" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D144" s="2">
-        <v>366</v>
+        <v>152</v>
       </c>
       <c r="E144" s="2">
-        <v>1346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D145" s="2">
-        <v>378</v>
+        <v>157</v>
       </c>
       <c r="E145" s="2">
-        <v>1442</v>
+        <v>379</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
       </c>
       <c r="C146" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D146" s="2">
-        <v>373</v>
+        <v>175</v>
       </c>
       <c r="E146" s="2">
-        <v>1258</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
       </c>
       <c r="C147" s="2">
+        <v>1</v>
+      </c>
+      <c r="D147" s="2">
+        <v>68</v>
+      </c>
+      <c r="E147" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C148" s="2">
+        <v>2</v>
+      </c>
+      <c r="D148" s="2">
+        <v>69</v>
+      </c>
+      <c r="E148" s="2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
+      <c r="A149" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C149" s="2">
         <v>3</v>
       </c>
-      <c r="D147" s="2">
+      <c r="D149" s="2">
+        <v>85</v>
+      </c>
+      <c r="E149" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" t="s">
+        <v>6</v>
+      </c>
+      <c r="B150" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C150" s="2">
+        <v>4</v>
+      </c>
+      <c r="D150" s="2">
+        <v>76</v>
+      </c>
+      <c r="E150" s="2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C151" s="2">
+        <v>1</v>
+      </c>
+      <c r="D151" s="2">
+        <v>378</v>
+      </c>
+      <c r="E151" s="2">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C152" s="2">
+        <v>2</v>
+      </c>
+      <c r="D152" s="2">
+        <v>373</v>
+      </c>
+      <c r="E152" s="2">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C153" s="2">
+        <v>3</v>
+      </c>
+      <c r="D153" s="2">
         <v>422</v>
       </c>
-      <c r="E147" s="2">
+      <c r="E153" s="2">
         <v>1455</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C154" s="2">
+        <v>4</v>
+      </c>
+      <c r="D154" s="2">
+        <v>397</v>
+      </c>
+      <c r="E154" s="2">
+        <v>1363</v>
       </c>
     </row>
   </sheetData>

--- a/upload/internacoes-via-urgencia.xlsx
+++ b/upload/internacoes-via-urgencia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7620"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="12">
   <si>
     <t>unidade</t>
   </si>
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2612,19 +2612,19 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B132" s="2">
         <v>2026</v>
       </c>
       <c r="C132" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D132" s="2">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="E132" s="2">
-        <v>254</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2635,13 +2635,13 @@
         <v>2026</v>
       </c>
       <c r="C133" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E133" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2652,13 +2652,13 @@
         <v>2026</v>
       </c>
       <c r="C134" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D134" s="2">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E134" s="2">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2669,47 +2669,47 @@
         <v>2026</v>
       </c>
       <c r="C135" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D135" s="2">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E135" s="2">
-        <v>310</v>
+        <v>256</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B136" s="2">
         <v>2026</v>
       </c>
       <c r="C136" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D136" s="2">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="E136" s="2">
-        <v>705</v>
+        <v>310</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B137" s="2">
         <v>2026</v>
       </c>
       <c r="C137" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D137" s="2">
-        <v>864</v>
+        <v>130</v>
       </c>
       <c r="E137" s="2">
-        <v>5010</v>
+        <v>309</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2720,64 +2720,64 @@
         <v>2026</v>
       </c>
       <c r="C138" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D138" s="2">
-        <v>776</v>
+        <v>93</v>
       </c>
       <c r="E138" s="2">
-        <v>5115</v>
+        <v>705</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
       </c>
       <c r="C139" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" s="2">
-        <v>264</v>
+        <v>862</v>
       </c>
       <c r="E139" s="2">
-        <v>2970</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
       </c>
       <c r="C140" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D140" s="2">
-        <v>304</v>
+        <v>775</v>
       </c>
       <c r="E140" s="2">
-        <v>2793</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
       </c>
       <c r="C141" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D141" s="2">
-        <v>293</v>
+        <v>795</v>
       </c>
       <c r="E141" s="2">
-        <v>3289</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2788,86 +2788,86 @@
         <v>2026</v>
       </c>
       <c r="C142" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D142" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E142" s="2">
-        <v>3405</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
       </c>
       <c r="C143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143" s="2">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="E143" s="2">
-        <v>404</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
       </c>
       <c r="C144" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="2">
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="E144" s="2">
-        <v>359</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
       </c>
       <c r="C145" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D145" s="2">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="E145" s="2">
-        <v>379</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
       </c>
       <c r="C146" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D146" s="2">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="E146" s="2">
-        <v>411</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
@@ -2876,15 +2876,15 @@
         <v>1</v>
       </c>
       <c r="D147" s="2">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="E147" s="2">
-        <v>248</v>
+        <v>404</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
@@ -2893,15 +2893,15 @@
         <v>2</v>
       </c>
       <c r="D148" s="2">
-        <v>69</v>
+        <v>152</v>
       </c>
       <c r="E148" s="2">
-        <v>249</v>
+        <v>359</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
@@ -2910,15 +2910,15 @@
         <v>3</v>
       </c>
       <c r="D149" s="2">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="E149" s="2">
-        <v>228</v>
+        <v>379</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
@@ -2927,78 +2927,197 @@
         <v>4</v>
       </c>
       <c r="D150" s="2">
-        <v>76</v>
+        <v>176</v>
       </c>
       <c r="E150" s="2">
-        <v>244</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
       </c>
       <c r="C151" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D151" s="2">
-        <v>378</v>
+        <v>168</v>
       </c>
       <c r="E151" s="2">
-        <v>1442</v>
+        <v>383</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
       </c>
       <c r="C152" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152" s="2">
-        <v>373</v>
+        <v>68</v>
       </c>
       <c r="E152" s="2">
-        <v>1258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
       </c>
       <c r="C153" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D153" s="2">
-        <v>422</v>
+        <v>69</v>
       </c>
       <c r="E153" s="2">
-        <v>1455</v>
+        <v>249</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
       </c>
       <c r="C154" s="2">
+        <v>3</v>
+      </c>
+      <c r="D154" s="2">
+        <v>85</v>
+      </c>
+      <c r="E154" s="2">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" t="s">
+        <v>6</v>
+      </c>
+      <c r="B155" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C155" s="2">
         <v>4</v>
       </c>
-      <c r="D154" s="2">
+      <c r="D155" s="2">
+        <v>73</v>
+      </c>
+      <c r="E155" s="2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" t="s">
+        <v>6</v>
+      </c>
+      <c r="B156" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C156" s="2">
+        <v>5</v>
+      </c>
+      <c r="D156" s="2">
+        <v>89</v>
+      </c>
+      <c r="E156" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C157" s="2">
+        <v>1</v>
+      </c>
+      <c r="D157" s="2">
+        <v>379</v>
+      </c>
+      <c r="E157" s="2">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C158" s="2">
+        <v>2</v>
+      </c>
+      <c r="D158" s="2">
+        <v>373</v>
+      </c>
+      <c r="E158" s="2">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" t="s">
+        <v>7</v>
+      </c>
+      <c r="B159" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C159" s="2">
+        <v>3</v>
+      </c>
+      <c r="D159" s="2">
+        <v>422</v>
+      </c>
+      <c r="E159" s="2">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
+      <c r="A160" t="s">
+        <v>7</v>
+      </c>
+      <c r="B160" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C160" s="2">
+        <v>4</v>
+      </c>
+      <c r="D160" s="2">
         <v>397</v>
       </c>
-      <c r="E154" s="2">
+      <c r="E160" s="2">
         <v>1363</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C161" s="2">
+        <v>5</v>
+      </c>
+      <c r="D161" s="2">
+        <v>405</v>
+      </c>
+      <c r="E161" s="2">
+        <v>1241</v>
       </c>
     </row>
   </sheetData>

--- a/upload/internacoes-via-urgencia.xlsx
+++ b/upload/internacoes-via-urgencia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="12">
   <si>
     <t>unidade</t>
   </si>
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2573,7 +2573,7 @@
         <v>69</v>
       </c>
       <c r="E129" s="2">
-        <v>2243</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -2629,19 +2629,19 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B133" s="2">
         <v>2026</v>
       </c>
       <c r="C133" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D133" s="2">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="E133" s="2">
-        <v>254</v>
+        <v>2823</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2652,13 +2652,13 @@
         <v>2026</v>
       </c>
       <c r="C134" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E134" s="2">
-        <v>271</v>
+        <v>254</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2669,13 +2669,13 @@
         <v>2026</v>
       </c>
       <c r="C135" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D135" s="2">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E135" s="2">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2686,13 +2686,13 @@
         <v>2026</v>
       </c>
       <c r="C136" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D136" s="2">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E136" s="2">
-        <v>310</v>
+        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2703,47 +2703,47 @@
         <v>2026</v>
       </c>
       <c r="C137" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D137" s="2">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E137" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B138" s="2">
         <v>2026</v>
       </c>
       <c r="C138" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D138" s="2">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="E138" s="2">
-        <v>705</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B139" s="2">
         <v>2026</v>
       </c>
       <c r="C139" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D139" s="2">
-        <v>862</v>
+        <v>129</v>
       </c>
       <c r="E139" s="2">
-        <v>5014</v>
+        <v>240</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2754,13 +2754,13 @@
         <v>2026</v>
       </c>
       <c r="C140" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D140" s="2">
-        <v>775</v>
+        <v>93</v>
       </c>
       <c r="E140" s="2">
-        <v>5116</v>
+        <v>705</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2771,64 +2771,64 @@
         <v>2026</v>
       </c>
       <c r="C141" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D141" s="2">
-        <v>795</v>
+        <v>862</v>
       </c>
       <c r="E141" s="2">
-        <v>5276</v>
+        <v>5014</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B142" s="2">
         <v>2026</v>
       </c>
       <c r="C142" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D142" s="2">
-        <v>264</v>
+        <v>774</v>
       </c>
       <c r="E142" s="2">
-        <v>2970</v>
+        <v>5116</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B143" s="2">
         <v>2026</v>
       </c>
       <c r="C143" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D143" s="2">
-        <v>304</v>
+        <v>794</v>
       </c>
       <c r="E143" s="2">
-        <v>2793</v>
+        <v>5276</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B144" s="2">
         <v>2026</v>
       </c>
       <c r="C144" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D144" s="2">
-        <v>293</v>
+        <v>871</v>
       </c>
       <c r="E144" s="2">
-        <v>3289</v>
+        <v>5218</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2839,13 +2839,13 @@
         <v>2026</v>
       </c>
       <c r="C145" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D145" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E145" s="2">
-        <v>3405</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2856,81 +2856,81 @@
         <v>2026</v>
       </c>
       <c r="C146" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D146" s="2">
-        <v>279</v>
+        <v>304</v>
       </c>
       <c r="E146" s="2">
-        <v>3116</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
       </c>
       <c r="C147" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147" s="2">
-        <v>157</v>
+        <v>293</v>
       </c>
       <c r="E147" s="2">
-        <v>404</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B148" s="2">
         <v>2026</v>
       </c>
       <c r="C148" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D148" s="2">
-        <v>152</v>
+        <v>263</v>
       </c>
       <c r="E148" s="2">
-        <v>359</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B149" s="2">
         <v>2026</v>
       </c>
       <c r="C149" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D149" s="2">
-        <v>157</v>
+        <v>281</v>
       </c>
       <c r="E149" s="2">
-        <v>379</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B150" s="2">
         <v>2026</v>
       </c>
       <c r="C150" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D150" s="2">
-        <v>176</v>
+        <v>278</v>
       </c>
       <c r="E150" s="2">
-        <v>411</v>
+        <v>2973</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2941,103 +2941,103 @@
         <v>2026</v>
       </c>
       <c r="C151" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D151" s="2">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E151" s="2">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
       </c>
       <c r="C152" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D152" s="2">
-        <v>68</v>
+        <v>152</v>
       </c>
       <c r="E152" s="2">
-        <v>248</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
       </c>
       <c r="C153" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D153" s="2">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="E153" s="2">
-        <v>249</v>
+        <v>379</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
       </c>
       <c r="C154" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D154" s="2">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="E154" s="2">
-        <v>228</v>
+        <v>411</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B155" s="2">
         <v>2026</v>
       </c>
       <c r="C155" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D155" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="E155" s="2">
-        <v>248</v>
+        <v>383</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B156" s="2">
         <v>2026</v>
       </c>
       <c r="C156" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D156" s="2">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="E156" s="2">
-        <v>262</v>
+        <v>427</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
@@ -3046,15 +3046,15 @@
         <v>1</v>
       </c>
       <c r="D157" s="2">
-        <v>379</v>
+        <v>68</v>
       </c>
       <c r="E157" s="2">
-        <v>1441</v>
+        <v>248</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
@@ -3063,15 +3063,15 @@
         <v>2</v>
       </c>
       <c r="D158" s="2">
-        <v>373</v>
+        <v>69</v>
       </c>
       <c r="E158" s="2">
-        <v>1258</v>
+        <v>249</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
@@ -3080,15 +3080,15 @@
         <v>3</v>
       </c>
       <c r="D159" s="2">
-        <v>422</v>
+        <v>85</v>
       </c>
       <c r="E159" s="2">
-        <v>1455</v>
+        <v>228</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
@@ -3097,15 +3097,15 @@
         <v>4</v>
       </c>
       <c r="D160" s="2">
-        <v>397</v>
+        <v>73</v>
       </c>
       <c r="E160" s="2">
-        <v>1363</v>
+        <v>248</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
@@ -3114,10 +3114,129 @@
         <v>5</v>
       </c>
       <c r="D161" s="2">
+        <v>89</v>
+      </c>
+      <c r="E161" s="2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" t="s">
+        <v>6</v>
+      </c>
+      <c r="B162" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C162" s="2">
+        <v>6</v>
+      </c>
+      <c r="D162" s="2">
+        <v>80</v>
+      </c>
+      <c r="E162" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C163" s="2">
+        <v>1</v>
+      </c>
+      <c r="D163" s="2">
+        <v>379</v>
+      </c>
+      <c r="E163" s="2">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C164" s="2">
+        <v>2</v>
+      </c>
+      <c r="D164" s="2">
+        <v>373</v>
+      </c>
+      <c r="E164" s="2">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C165" s="2">
+        <v>3</v>
+      </c>
+      <c r="D165" s="2">
+        <v>422</v>
+      </c>
+      <c r="E165" s="2">
+        <v>1455</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C166" s="2">
+        <v>4</v>
+      </c>
+      <c r="D166" s="2">
+        <v>397</v>
+      </c>
+      <c r="E166" s="2">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C167" s="2">
+        <v>5</v>
+      </c>
+      <c r="D167" s="2">
         <v>405</v>
       </c>
-      <c r="E161" s="2">
+      <c r="E167" s="2">
         <v>1241</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C168" s="2">
+        <v>6</v>
+      </c>
+      <c r="D168" s="2">
+        <v>382</v>
+      </c>
+      <c r="E168" s="2">
+        <v>1203</v>
       </c>
     </row>
   </sheetData>

--- a/upload/internacoes-via-urgencia.xlsx
+++ b/upload/internacoes-via-urgencia.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Export" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="12">
   <si>
     <t>unidade</t>
   </si>
@@ -380,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E168"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -564,10 +564,10 @@
         <v>4</v>
       </c>
       <c r="D11" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E11" s="2">
-        <v>1061</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -581,10 +581,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="E12" s="2">
-        <v>1358</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -598,10 +598,10 @@
         <v>6</v>
       </c>
       <c r="D13" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E13" s="2">
-        <v>1258</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -615,10 +615,10 @@
         <v>7</v>
       </c>
       <c r="D14" s="2">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2">
-        <v>1266</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -632,10 +632,10 @@
         <v>8</v>
       </c>
       <c r="D15" s="2">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="E15" s="2">
-        <v>1443</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -649,10 +649,10 @@
         <v>9</v>
       </c>
       <c r="D16" s="2">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E16" s="2">
-        <v>1392</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -666,10 +666,10 @@
         <v>10</v>
       </c>
       <c r="D17" s="2">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="E17" s="2">
-        <v>1500</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -683,10 +683,10 @@
         <v>11</v>
       </c>
       <c r="D18" s="2">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="E18" s="2">
-        <v>1424</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -700,10 +700,10 @@
         <v>12</v>
       </c>
       <c r="D19" s="2">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="E19" s="2">
-        <v>1304</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1278,10 +1278,10 @@
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="E53" s="2">
-        <v>1534</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1295,10 +1295,10 @@
         <v>2</v>
       </c>
       <c r="D54" s="2">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="E54" s="2">
-        <v>1510</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1312,10 +1312,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="2">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="E55" s="2">
-        <v>1540</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -1329,10 +1329,10 @@
         <v>4</v>
       </c>
       <c r="D56" s="2">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="E56" s="2">
-        <v>1402</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -1346,10 +1346,10 @@
         <v>5</v>
       </c>
       <c r="D57" s="2">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="E57" s="2">
-        <v>1363</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1363,10 +1363,10 @@
         <v>6</v>
       </c>
       <c r="D58" s="2">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="E58" s="2">
-        <v>1129</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1380,10 +1380,10 @@
         <v>7</v>
       </c>
       <c r="D59" s="2">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="E59" s="2">
-        <v>1262</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1397,10 +1397,10 @@
         <v>8</v>
       </c>
       <c r="D60" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="E60" s="2">
-        <v>1257</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1414,10 +1414,10 @@
         <v>9</v>
       </c>
       <c r="D61" s="2">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="E61" s="2">
-        <v>1297</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1431,10 +1431,10 @@
         <v>10</v>
       </c>
       <c r="D62" s="2">
-        <v>357</v>
+        <v>333</v>
       </c>
       <c r="E62" s="2">
-        <v>1315</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1448,10 +1448,10 @@
         <v>11</v>
       </c>
       <c r="D63" s="2">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="E63" s="2">
-        <v>1329</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1465,10 +1465,10 @@
         <v>12</v>
       </c>
       <c r="D64" s="2">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="E64" s="2">
-        <v>1261</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2349,10 +2349,10 @@
         <v>1</v>
       </c>
       <c r="D116" s="2">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="E116" s="2">
-        <v>1450</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2366,10 +2366,10 @@
         <v>2</v>
       </c>
       <c r="D117" s="2">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="E117" s="2">
-        <v>1356</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2383,10 +2383,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="2">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="E118" s="2">
-        <v>1578</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2400,10 +2400,10 @@
         <v>4</v>
       </c>
       <c r="D119" s="2">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="E119" s="2">
-        <v>1524</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -2417,10 +2417,10 @@
         <v>5</v>
       </c>
       <c r="D120" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E120" s="2">
-        <v>1432</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2434,10 +2434,10 @@
         <v>6</v>
       </c>
       <c r="D121" s="2">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="E121" s="2">
-        <v>1308</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2451,10 +2451,10 @@
         <v>7</v>
       </c>
       <c r="D122" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E122" s="2">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2468,10 +2468,10 @@
         <v>8</v>
       </c>
       <c r="D123" s="2">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="E123" s="2">
-        <v>1401</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2485,10 +2485,10 @@
         <v>9</v>
       </c>
       <c r="D124" s="2">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="E124" s="2">
-        <v>1377</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2502,10 +2502,10 @@
         <v>10</v>
       </c>
       <c r="D125" s="2">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="E125" s="2">
-        <v>1446</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2519,10 +2519,10 @@
         <v>11</v>
       </c>
       <c r="D126" s="2">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="E126" s="2">
-        <v>1359</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2536,10 +2536,10 @@
         <v>12</v>
       </c>
       <c r="D127" s="2">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="E127" s="2">
-        <v>1346</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2638,27 +2638,27 @@
         <v>6</v>
       </c>
       <c r="D133" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E133" s="2">
-        <v>2823</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B134" s="2">
         <v>2026</v>
       </c>
       <c r="C134" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D134" s="2">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="E134" s="2">
-        <v>254</v>
+        <v>2638</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2669,13 +2669,13 @@
         <v>2026</v>
       </c>
       <c r="C135" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D135" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E135" s="2">
-        <v>272</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2686,13 +2686,13 @@
         <v>2026</v>
       </c>
       <c r="C136" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" s="2">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="E136" s="2">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2703,13 +2703,13 @@
         <v>2026</v>
       </c>
       <c r="C137" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D137" s="2">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E137" s="2">
-        <v>311</v>
+        <v>257</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2720,13 +2720,13 @@
         <v>2026</v>
       </c>
       <c r="C138" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D138" s="2">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E138" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2737,47 +2737,47 @@
         <v>2026</v>
       </c>
       <c r="C139" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D139" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E139" s="2">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B140" s="2">
         <v>2026</v>
       </c>
       <c r="C140" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D140" s="2">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="E140" s="2">
-        <v>705</v>
+        <v>241</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B141" s="2">
         <v>2026</v>
       </c>
       <c r="C141" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D141" s="2">
-        <v>862</v>
+        <v>133</v>
       </c>
       <c r="E141" s="2">
-        <v>5014</v>
+        <v>317</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2788,13 +2788,13 @@
         <v>2026</v>
       </c>
       <c r="C142" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D142" s="2">
-        <v>774</v>
+        <v>93</v>
       </c>
       <c r="E142" s="2">
-        <v>5116</v>
+        <v>705</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2805,13 +2805,13 @@
         <v>2026</v>
       </c>
       <c r="C143" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D143" s="2">
-        <v>794</v>
+        <v>861</v>
       </c>
       <c r="E143" s="2">
-        <v>5276</v>
+        <v>5015</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2822,64 +2822,64 @@
         <v>2026</v>
       </c>
       <c r="C144" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D144" s="2">
-        <v>871</v>
+        <v>772</v>
       </c>
       <c r="E144" s="2">
-        <v>5218</v>
+        <v>5118</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B145" s="2">
         <v>2026</v>
       </c>
       <c r="C145" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D145" s="2">
-        <v>264</v>
+        <v>793</v>
       </c>
       <c r="E145" s="2">
-        <v>2970</v>
+        <v>5277</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B146" s="2">
         <v>2026</v>
       </c>
       <c r="C146" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D146" s="2">
-        <v>304</v>
+        <v>870</v>
       </c>
       <c r="E146" s="2">
-        <v>2793</v>
+        <v>5220</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B147" s="2">
         <v>2026</v>
       </c>
       <c r="C147" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D147" s="2">
-        <v>293</v>
+        <v>838</v>
       </c>
       <c r="E147" s="2">
-        <v>3289</v>
+        <v>5561</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2890,13 +2890,13 @@
         <v>2026</v>
       </c>
       <c r="C148" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D148" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E148" s="2">
-        <v>3405</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2907,13 +2907,13 @@
         <v>2026</v>
       </c>
       <c r="C149" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D149" s="2">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="E149" s="2">
-        <v>3114</v>
+        <v>2793</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2924,81 +2924,81 @@
         <v>2026</v>
       </c>
       <c r="C150" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D150" s="2">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="E150" s="2">
-        <v>2973</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B151" s="2">
         <v>2026</v>
       </c>
       <c r="C151" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D151" s="2">
-        <v>157</v>
+        <v>263</v>
       </c>
       <c r="E151" s="2">
-        <v>404</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B152" s="2">
         <v>2026</v>
       </c>
       <c r="C152" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D152" s="2">
-        <v>152</v>
+        <v>281</v>
       </c>
       <c r="E152" s="2">
-        <v>359</v>
+        <v>3114</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B153" s="2">
         <v>2026</v>
       </c>
       <c r="C153" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D153" s="2">
-        <v>157</v>
+        <v>282</v>
       </c>
       <c r="E153" s="2">
-        <v>379</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B154" s="2">
         <v>2026</v>
       </c>
       <c r="C154" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D154" s="2">
-        <v>176</v>
+        <v>264</v>
       </c>
       <c r="E154" s="2">
-        <v>411</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -3009,13 +3009,13 @@
         <v>2026</v>
       </c>
       <c r="C155" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D155" s="2">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E155" s="2">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3026,98 +3026,98 @@
         <v>2026</v>
       </c>
       <c r="C156" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D156" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E156" s="2">
-        <v>427</v>
+        <v>359</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B157" s="2">
         <v>2026</v>
       </c>
       <c r="C157" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D157" s="2">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="E157" s="2">
-        <v>248</v>
+        <v>379</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B158" s="2">
         <v>2026</v>
       </c>
       <c r="C158" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D158" s="2">
-        <v>69</v>
+        <v>176</v>
       </c>
       <c r="E158" s="2">
-        <v>249</v>
+        <v>411</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B159" s="2">
         <v>2026</v>
       </c>
       <c r="C159" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D159" s="2">
-        <v>85</v>
+        <v>168</v>
       </c>
       <c r="E159" s="2">
-        <v>228</v>
+        <v>383</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B160" s="2">
         <v>2026</v>
       </c>
       <c r="C160" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D160" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="E160" s="2">
-        <v>248</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B161" s="2">
         <v>2026</v>
       </c>
       <c r="C161" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D161" s="2">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="E161" s="2">
-        <v>262</v>
+        <v>360</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3128,115 +3128,234 @@
         <v>2026</v>
       </c>
       <c r="C162" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D162" s="2">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E162" s="2">
-        <v>226</v>
+        <v>248</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B163" s="2">
         <v>2026</v>
       </c>
       <c r="C163" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" s="2">
-        <v>379</v>
+        <v>69</v>
       </c>
       <c r="E163" s="2">
-        <v>1441</v>
+        <v>249</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B164" s="2">
         <v>2026</v>
       </c>
       <c r="C164" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D164" s="2">
-        <v>373</v>
+        <v>85</v>
       </c>
       <c r="E164" s="2">
-        <v>1258</v>
+        <v>228</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B165" s="2">
         <v>2026</v>
       </c>
       <c r="C165" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D165" s="2">
-        <v>422</v>
+        <v>73</v>
       </c>
       <c r="E165" s="2">
-        <v>1455</v>
+        <v>248</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B166" s="2">
         <v>2026</v>
       </c>
       <c r="C166" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D166" s="2">
-        <v>397</v>
+        <v>89</v>
       </c>
       <c r="E166" s="2">
-        <v>1363</v>
+        <v>262</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B167" s="2">
         <v>2026</v>
       </c>
       <c r="C167" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D167" s="2">
-        <v>405</v>
+        <v>79</v>
       </c>
       <c r="E167" s="2">
-        <v>1241</v>
+        <v>227</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B168" s="2">
         <v>2026</v>
       </c>
       <c r="C168" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D168" s="2">
-        <v>382</v>
+        <v>86</v>
       </c>
       <c r="E168" s="2">
-        <v>1203</v>
+        <v>228</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C169" s="2">
+        <v>1</v>
+      </c>
+      <c r="D169" s="2">
+        <v>359</v>
+      </c>
+      <c r="E169" s="2">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C170" s="2">
+        <v>2</v>
+      </c>
+      <c r="D170" s="2">
+        <v>353</v>
+      </c>
+      <c r="E170" s="2">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C171" s="2">
+        <v>3</v>
+      </c>
+      <c r="D171" s="2">
+        <v>404</v>
+      </c>
+      <c r="E171" s="2">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C172" s="2">
+        <v>4</v>
+      </c>
+      <c r="D172" s="2">
+        <v>380</v>
+      </c>
+      <c r="E172" s="2">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C173" s="2">
+        <v>5</v>
+      </c>
+      <c r="D173" s="2">
+        <v>381</v>
+      </c>
+      <c r="E173" s="2">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C174" s="2">
+        <v>6</v>
+      </c>
+      <c r="D174" s="2">
+        <v>355</v>
+      </c>
+      <c r="E174" s="2">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="2">
+        <v>2026</v>
+      </c>
+      <c r="C175" s="2">
+        <v>7</v>
+      </c>
+      <c r="D175" s="2">
+        <v>349</v>
+      </c>
+      <c r="E175" s="2">
+        <v>1466</v>
       </c>
     </row>
   </sheetData>
